--- a/reports/Debug-purgatory-20260106/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Week Ending (Actual)_Visits.xlsx
@@ -37,10 +37,10 @@
     <t>Purgatory Comp Tickets</t>
   </si>
   <si>
+    <t>Purgatory Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C2" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C3" s="2">
-        <v>322</v>
+        <v>258</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C4" s="2">
-        <v>97</v>
+        <v>564</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C6" s="2">
-        <v>568</v>
+        <v>322</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,7 +504,7 @@
         <v>46028</v>
       </c>
       <c r="C7" s="2">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,7 +518,7 @@
         <v>46027</v>
       </c>
       <c r="C8" s="2">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -529,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,10 +557,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -574,10 +574,10 @@
         <v>46028</v>
       </c>
       <c r="C12" s="2">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +585,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C13" s="2">
-        <v>67</v>
+        <v>1415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C15" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,10 +644,10 @@
         <v>46027</v>
       </c>
       <c r="C17" s="2">
-        <v>1407</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,7 +658,7 @@
         <v>46027</v>
       </c>
       <c r="C18" s="2">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,7 +672,7 @@
         <v>46028</v>
       </c>
       <c r="C19" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -683,10 +683,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>46027</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>1407</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,7 +714,7 @@
         <v>46027</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -728,7 +728,7 @@
         <v>46028</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -742,10 +742,10 @@
         <v>46028</v>
       </c>
       <c r="C24" s="2">
-        <v>1416</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
